--- a/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Smoking Status Observation, ResourceType Observation</t>
+    <t>This StructureDefinition contains the maps for VistA V HEALTH FACTORS (file 9000010.23) to FHIR Observation</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3135" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3134" uniqueCount="563">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1191,10 +1191,7 @@
     <t>Coded Responses from Smoking Status Value Set</t>
   </si>
   <si>
-    <t>This value set enumerates codes SNOMED CT codes historically used for the current smoking status of a patient with a maximum required binding to Snomed CT codes.</t>
-  </si>
-  <si>
-    <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113883.11.20.9.38</t>
+    <t>http://va.gov/fhir/ValueSet/VFSmokingStatus</t>
   </si>
   <si>
     <t>1249: terminologyMaps using VF_SmokingStatus on V HEALTH FACTOR - HEALTH FACTOR (#9000010.23-.01)</t>
@@ -2121,7 +2118,7 @@
     <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="156.046875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="72.8984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="14.109375" customWidth="true" bestFit="true"/>
@@ -7646,13 +7643,11 @@
         <v>40</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y44" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="Y44" s="2"/>
+      <c r="Z44" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>40</v>
@@ -7706,15 +7701,15 @@
         <v>40</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7740,16 +7735,16 @@
         <v>139</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>40</v>
@@ -7777,11 +7772,11 @@
         <v>144</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>385</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>40</v>
       </c>
@@ -7798,7 +7793,7 @@
         <v>40</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>38</v>
@@ -7807,7 +7802,7 @@
         <v>50</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>62</v>
@@ -7822,7 +7817,7 @@
         <v>93</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>40</v>
@@ -7839,14 +7834,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7868,16 +7863,16 @@
         <v>139</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>40</v>
@@ -7905,11 +7900,11 @@
         <v>144</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>395</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>40</v>
       </c>
@@ -7926,7 +7921,7 @@
         <v>40</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>38</v>
@@ -7944,19 +7939,19 @@
         <v>40</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>40</v>
@@ -7967,10 +7962,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7993,19 +7988,19 @@
         <v>40</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>40</v>
@@ -8054,7 +8049,7 @@
         <v>40</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>38</v>
@@ -8075,10 +8070,10 @@
         <v>40</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>40</v>
@@ -8095,10 +8090,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8219,10 +8214,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8345,10 +8340,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8371,16 +8366,16 @@
         <v>51</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8430,7 +8425,7 @@
         <v>40</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>38</v>
@@ -8454,7 +8449,7 @@
         <v>93</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>40</v>
@@ -8471,10 +8466,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8500,10 +8495,10 @@
         <v>330</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8554,7 +8549,7 @@
         <v>40</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>38</v>
@@ -8578,7 +8573,7 @@
         <v>93</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>40</v>
@@ -8595,10 +8590,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8621,13 +8616,13 @@
         <v>51</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8678,7 +8673,7 @@
         <v>40</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>50</v>
@@ -8702,27 +8697,27 @@
         <v>93</v>
       </c>
       <c r="AN52" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP52" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ52" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AO52" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AQ52" t="s" s="2">
+      <c r="AR52" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AR52" t="s" s="2">
-        <v>429</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8748,13 +8743,13 @@
         <v>139</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8780,14 +8775,14 @@
         <v>40</v>
       </c>
       <c r="X53" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="Y53" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="Y53" t="s" s="2">
+      <c r="Z53" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="Z53" t="s" s="2">
-        <v>436</v>
-      </c>
       <c r="AA53" t="s" s="2">
         <v>40</v>
       </c>
@@ -8804,7 +8799,7 @@
         <v>40</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>38</v>
@@ -8822,19 +8817,19 @@
         <v>40</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>40</v>
@@ -8845,10 +8840,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8874,16 +8869,16 @@
         <v>139</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>40</v>
@@ -8908,14 +8903,14 @@
         <v>40</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Y54" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z54" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="Z54" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AA54" t="s" s="2">
         <v>40</v>
       </c>
@@ -8932,7 +8927,7 @@
         <v>40</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>38</v>
@@ -8953,10 +8948,10 @@
         <v>40</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>40</v>
@@ -8973,10 +8968,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8999,16 +8994,16 @@
         <v>40</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9058,7 +9053,7 @@
         <v>40</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>38</v>
@@ -9076,19 +9071,19 @@
         <v>40</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>40</v>
@@ -9099,10 +9094,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9125,16 +9120,16 @@
         <v>40</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9184,7 +9179,7 @@
         <v>40</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>38</v>
@@ -9202,19 +9197,19 @@
         <v>40</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>40</v>
@@ -9225,10 +9220,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9251,19 +9246,19 @@
         <v>40</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>40</v>
@@ -9312,7 +9307,7 @@
         <v>40</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>38</v>
@@ -9324,19 +9319,19 @@
         <v>40</v>
       </c>
       <c r="AJ57" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="AK57" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>40</v>
@@ -9353,10 +9348,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9477,10 +9472,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9603,14 +9598,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9632,10 +9627,10 @@
         <v>96</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>99</v>
@@ -9690,7 +9685,7 @@
         <v>40</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>38</v>
@@ -9731,10 +9726,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9757,13 +9752,13 @@
         <v>40</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9814,7 +9809,7 @@
         <v>40</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>38</v>
@@ -9823,7 +9818,7 @@
         <v>50</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>62</v>
@@ -9835,10 +9830,10 @@
         <v>40</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>40</v>
@@ -9855,10 +9850,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9881,13 +9876,13 @@
         <v>40</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9938,7 +9933,7 @@
         <v>40</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>38</v>
@@ -9947,7 +9942,7 @@
         <v>50</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>62</v>
@@ -9959,10 +9954,10 @@
         <v>40</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>40</v>
@@ -9979,10 +9974,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10008,16 +10003,16 @@
         <v>139</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>40</v>
@@ -10045,11 +10040,11 @@
         <v>74</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>501</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>40</v>
       </c>
@@ -10066,7 +10061,7 @@
         <v>40</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>38</v>
@@ -10084,13 +10079,13 @@
         <v>40</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AM63" t="s" s="2">
-        <v>503</v>
-      </c>
       <c r="AN63" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>40</v>
@@ -10107,10 +10102,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10136,16 +10131,16 @@
         <v>139</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>40</v>
@@ -10170,14 +10165,14 @@
         <v>40</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="Z64" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>510</v>
-      </c>
       <c r="AA64" t="s" s="2">
         <v>40</v>
       </c>
@@ -10194,7 +10189,7 @@
         <v>40</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>38</v>
@@ -10212,13 +10207,13 @@
         <v>40</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AM64" t="s" s="2">
-        <v>503</v>
-      </c>
       <c r="AN64" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>40</v>
@@ -10235,10 +10230,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10261,17 +10256,17 @@
         <v>40</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>40</v>
@@ -10320,7 +10315,7 @@
         <v>40</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>38</v>
@@ -10344,7 +10339,7 @@
         <v>40</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>40</v>
@@ -10361,10 +10356,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10390,10 +10385,10 @@
         <v>117</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10444,7 +10439,7 @@
         <v>40</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>38</v>
@@ -10465,10 +10460,10 @@
         <v>40</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>40</v>
@@ -10485,10 +10480,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10511,16 +10506,16 @@
         <v>51</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10570,7 +10565,7 @@
         <v>40</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>38</v>
@@ -10591,10 +10586,10 @@
         <v>40</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>40</v>
@@ -10611,10 +10606,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10637,16 +10632,16 @@
         <v>51</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10696,7 +10691,7 @@
         <v>40</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>38</v>
@@ -10717,10 +10712,10 @@
         <v>40</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>40</v>
@@ -10737,10 +10732,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10763,19 +10758,19 @@
         <v>51</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>40</v>
@@ -10824,7 +10819,7 @@
         <v>40</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>38</v>
@@ -10845,10 +10840,10 @@
         <v>40</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>40</v>
@@ -10865,10 +10860,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10989,10 +10984,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11115,14 +11110,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11144,10 +11139,10 @@
         <v>96</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>99</v>
@@ -11202,7 +11197,7 @@
         <v>40</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>38</v>
@@ -11243,10 +11238,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11272,13 +11267,13 @@
         <v>139</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>290</v>
@@ -11306,14 +11301,14 @@
         <v>40</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="Z73" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>549</v>
-      </c>
       <c r="AA73" t="s" s="2">
         <v>40</v>
       </c>
@@ -11330,7 +11325,7 @@
         <v>40</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>50</v>
@@ -11348,7 +11343,7 @@
         <v>40</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>294</v>
@@ -11371,10 +11366,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11397,16 +11392,16 @@
         <v>51</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="M74" t="s" s="2">
         <v>365</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>367</v>
@@ -11458,7 +11453,7 @@
         <v>40</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>38</v>
@@ -11476,7 +11471,7 @@
         <v>40</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>370</v>
@@ -11499,10 +11494,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11528,16 +11523,16 @@
         <v>139</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="N75" t="s" s="2">
-        <v>559</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>40</v>
@@ -11565,11 +11560,11 @@
         <v>144</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>385</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>40</v>
       </c>
@@ -11586,7 +11581,7 @@
         <v>40</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>38</v>
@@ -11595,7 +11590,7 @@
         <v>50</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>62</v>
@@ -11610,7 +11605,7 @@
         <v>93</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>40</v>
@@ -11627,14 +11622,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11656,16 +11651,16 @@
         <v>139</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>40</v>
@@ -11693,11 +11688,11 @@
         <v>144</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="Z76" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="Z76" t="s" s="2">
-        <v>395</v>
-      </c>
       <c r="AA76" t="s" s="2">
         <v>40</v>
       </c>
@@ -11714,7 +11709,7 @@
         <v>40</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>38</v>
@@ -11732,19 +11727,19 @@
         <v>40</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>40</v>
@@ -11755,10 +11750,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11784,16 +11779,16 @@
         <v>41</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="M77" t="s" s="2">
-        <v>563</v>
-      </c>
       <c r="N77" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="O77" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>40</v>
@@ -11842,7 +11837,7 @@
         <v>40</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>38</v>
@@ -11863,10 +11858,10 @@
         <v>40</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>40</v>

--- a/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3178" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3178" uniqueCount="609">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -255,10 +255,10 @@
     <t>Mapping: SNOMED CT Attribute Binding</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -794,6 +794,10 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-observation-smoking-status-status</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-28:1242: fixed value "final" {null}</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -941,6 +945,10 @@
   </si>
   <si>
     <t>Coding.code</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-29:1243: fixed value "social-history" {null}</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1167,10 +1175,10 @@
     <t>FiveWs.context</t>
   </si>
   <si>
+    <t>1246: reference from V HEALTH FACTOR - VISIT (#9000010.23-.03)</t>
+  </si>
+  <si>
     <t>HF.HealthFactor.VisitDateTime</t>
-  </si>
-  <si>
-    <t>1246: reference from V HEALTH FACTOR - VISIT (#9000010.23-.03)</t>
   </si>
   <si>
     <t>Observation.effective[x]</t>
@@ -1221,10 +1229,10 @@
     <t>effectiveDateTime</t>
   </si>
   <si>
+    <t>1247: source value from V HEALTH FACTOR - EVENT DATE AND TIME (#9000010.23-1201)</t>
+  </si>
+  <si>
     <t>HF.HealthFactor.EventDateTime</t>
-  </si>
-  <si>
-    <t>1247: source value from V HEALTH FACTOR - EVENT DATE AND TIME (#9000010.23-1201)</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1482,10 +1490,10 @@
     <t>Act.text</t>
   </si>
   <si>
+    <t>1250: source value from V HEALTH FACTOR - COMMENTS (#9000010.23-81101)</t>
+  </si>
+  <si>
     <t>HF.HealthFactor.Comments</t>
-  </si>
-  <si>
-    <t>1250: source value from V HEALTH FACTOR - COMMENTS (#9000010.23-81101)</t>
   </si>
   <si>
     <t>Observation.bodySite</t>
@@ -2269,8 +2277,8 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="101.90625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="101.90625" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4421,10 +4429,10 @@
         <v>84</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>210</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -5028,39 +5036,39 @@
         <v>84</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>106</v>
+        <v>250</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>84</v>
+        <v>256</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>255</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5086,16 +5094,16 @@
         <v>183</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -5123,16 +5131,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5142,7 +5150,7 @@
         <v>170</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5166,10 +5174,10 @@
         <v>84</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>84</v>
@@ -5183,10 +5191,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5307,10 +5315,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5433,10 +5441,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5459,19 +5467,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5520,7 +5528,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5541,10 +5549,10 @@
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>84</v>
@@ -5561,10 +5569,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5685,10 +5693,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5811,10 +5819,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5840,16 +5848,16 @@
         <v>108</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5898,7 +5906,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5919,10 +5927,10 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>84</v>
@@ -5939,10 +5947,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5968,13 +5976,13 @@
         <v>161</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6024,7 +6032,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6045,10 +6053,10 @@
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>84</v>
@@ -6065,10 +6073,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6094,14 +6102,14 @@
         <v>114</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -6150,7 +6158,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6162,7 +6170,7 @@
         <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>300</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>84</v>
@@ -6171,10 +6179,10 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>84</v>
@@ -6183,18 +6191,18 @@
         <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>84</v>
+        <v>303</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>301</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6220,14 +6228,14 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6276,7 +6284,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6297,10 +6305,10 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>84</v>
@@ -6317,10 +6325,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6343,19 +6351,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6404,7 +6412,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6425,10 +6433,10 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>84</v>
@@ -6445,10 +6453,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6474,16 +6482,16 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6532,7 +6540,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6553,10 +6561,10 @@
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>84</v>
@@ -6573,13 +6581,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>84</v>
@@ -6604,16 +6612,16 @@
         <v>183</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6623,7 +6631,7 @@
         <v>84</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>84</v>
@@ -6641,10 +6649,10 @@
         <v>118</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>84</v>
@@ -6662,7 +6670,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6686,10 +6694,10 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>84</v>
@@ -6703,14 +6711,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6732,16 +6740,16 @@
         <v>183</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6770,7 +6778,7 @@
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -6788,7 +6796,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>94</v>
@@ -6803,22 +6811,22 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6829,10 +6837,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6855,19 +6863,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6916,7 +6924,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6931,36 +6939,36 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>84</v>
+        <v>354</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>352</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6983,16 +6991,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7042,7 +7050,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7063,13 +7071,13 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>84</v>
@@ -7083,14 +7091,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7109,19 +7117,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7170,7 +7178,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7185,40 +7193,40 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7237,19 +7245,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7286,17 +7294,17 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7311,19 +7319,19 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>84</v>
@@ -7337,16 +7345,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7365,19 +7373,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7426,7 +7434,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7441,36 +7449,36 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7493,16 +7501,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7552,7 +7560,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7573,13 +7581,13 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>84</v>
@@ -7593,10 +7601,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7619,17 +7627,17 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7678,7 +7686,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7693,36 +7701,36 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>84</v>
+        <v>408</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>406</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7748,16 +7756,16 @@
         <v>183</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7794,17 +7802,17 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7813,7 +7821,7 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
@@ -7822,19 +7830,19 @@
         <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7845,13 +7853,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>84</v>
@@ -7876,16 +7884,16 @@
         <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7914,7 +7922,7 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7932,7 +7940,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7941,7 +7949,7 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7950,33 +7958,33 @@
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>84</v>
+        <v>423</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>421</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8002,16 +8010,16 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8039,10 +8047,10 @@
         <v>188</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8060,7 +8068,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8069,7 +8077,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -8084,7 +8092,7 @@
         <v>137</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -8101,14 +8109,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8130,16 +8138,16 @@
         <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8167,10 +8175,10 @@
         <v>188</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8188,7 +8196,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8206,19 +8214,19 @@
         <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8229,10 +8237,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8255,19 +8263,19 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8316,7 +8324,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8337,10 +8345,10 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
@@ -8357,10 +8365,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8481,10 +8489,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8607,10 +8615,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8633,16 +8641,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8692,7 +8700,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8716,7 +8724,7 @@
         <v>137</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
@@ -8733,10 +8741,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8759,13 +8767,13 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8816,7 +8824,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8840,7 +8848,7 @@
         <v>137</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
@@ -8857,10 +8865,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8883,13 +8891,13 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8940,7 +8948,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>94</v>
@@ -8964,7 +8972,7 @@
         <v>137</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -8973,18 +8981,18 @@
         <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9010,13 +9018,13 @@
         <v>183</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9042,13 +9050,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9066,7 +9074,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9084,19 +9092,19 @@
         <v>84</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -9107,10 +9115,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9136,16 +9144,16 @@
         <v>183</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9170,13 +9178,13 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -9194,7 +9202,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9215,10 +9223,10 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
@@ -9235,10 +9243,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9261,16 +9269,16 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9320,7 +9328,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9338,19 +9346,19 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9361,10 +9369,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9387,16 +9395,16 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9446,7 +9454,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9464,19 +9472,19 @@
         <v>84</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9487,10 +9495,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9513,19 +9521,19 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9574,7 +9582,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9586,7 +9594,7 @@
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -9595,10 +9603,10 @@
         <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>84</v>
@@ -9615,10 +9623,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9739,10 +9747,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9865,14 +9873,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9894,10 +9902,10 @@
         <v>140</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>143</v>
@@ -9952,7 +9960,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9993,10 +10001,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10019,13 +10027,13 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10076,7 +10084,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10085,7 +10093,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -10097,10 +10105,10 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
@@ -10117,10 +10125,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10143,13 +10151,13 @@
         <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10200,7 +10208,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10209,7 +10217,7 @@
         <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>106</v>
@@ -10221,10 +10229,10 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
@@ -10241,10 +10249,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10270,16 +10278,16 @@
         <v>183</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10307,10 +10315,10 @@
         <v>118</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10328,7 +10336,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10346,13 +10354,13 @@
         <v>84</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10369,10 +10377,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10398,16 +10406,16 @@
         <v>183</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10432,13 +10440,13 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10456,7 +10464,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10474,13 +10482,13 @@
         <v>84</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>84</v>
@@ -10497,10 +10505,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10523,17 +10531,17 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -10582,7 +10590,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10606,7 +10614,7 @@
         <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>84</v>
@@ -10623,10 +10631,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10652,10 +10660,10 @@
         <v>161</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10706,7 +10714,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10727,10 +10735,10 @@
         <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
@@ -10747,10 +10755,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10773,16 +10781,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10832,7 +10840,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10853,10 +10861,10 @@
         <v>84</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
@@ -10873,10 +10881,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10899,16 +10907,16 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10958,7 +10966,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10979,10 +10987,10 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>84</v>
@@ -10999,10 +11007,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11025,19 +11033,19 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11086,7 +11094,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11107,10 +11115,10 @@
         <v>84</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>84</v>
@@ -11127,10 +11135,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11251,10 +11259,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11377,14 +11385,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11406,10 +11414,10 @@
         <v>140</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>143</v>
@@ -11464,7 +11472,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11505,10 +11513,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11534,16 +11542,16 @@
         <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -11568,13 +11576,13 @@
         <v>84</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -11592,7 +11600,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>94</v>
@@ -11610,16 +11618,16 @@
         <v>84</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>84</v>
@@ -11633,10 +11641,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11659,19 +11667,19 @@
         <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -11720,7 +11728,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11738,19 +11746,19 @@
         <v>84</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -11761,10 +11769,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11790,16 +11798,16 @@
         <v>183</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
@@ -11827,10 +11835,10 @@
         <v>188</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -11848,7 +11856,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -11857,7 +11865,7 @@
         <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>106</v>
@@ -11872,7 +11880,7 @@
         <v>137</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>84</v>
@@ -11889,14 +11897,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11918,16 +11926,16 @@
         <v>183</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -11955,10 +11963,10 @@
         <v>188</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -11976,7 +11984,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -11994,19 +12002,19 @@
         <v>84</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12017,10 +12025,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12046,16 +12054,16 @@
         <v>85</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12104,7 +12112,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12125,10 +12133,10 @@
         <v>84</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -795,7 +795,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-28:1242: fixed value "final" {null}</t>
+inv-34:1242: fixed value = final {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -948,7 +948,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-29:1243: fixed value "social-history" {null}</t>
+inv-35:1243: fixed value = social-history {null}</t>
   </si>
   <si>
     <t>C*E.1</t>

--- a/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -795,7 +795,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-34:1242: fixed value = final {null}</t>
+inv-32:1242: fixed value = final {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -948,7 +948,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-35:1243: fixed value = social-history {null}</t>
+inv-33:1243: fixed value = social-history {null}</t>
   </si>
   <si>
     <t>C*E.1</t>

--- a/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -795,7 +795,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-32:1242: fixed value = final {null}</t>
+inv-34:1242: fixed value = final {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -948,7 +948,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-33:1243: fixed value = social-history {null}</t>
+inv-35:1243: fixed value = social-history {null}</t>
   </si>
   <si>
     <t>C*E.1</t>

--- a/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -795,7 +795,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-34:1242: fixed value = final {null}</t>
+inv-35:1242: fixed value = final {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -948,7 +948,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-35:1243: fixed value = social-history {null}</t>
+inv-36:1243: fixed value = social-history {null}</t>
   </si>
   <si>
     <t>C*E.1</t>

--- a/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA V HEALTH FACTORS (file 9000010.23) to FHIR Observation</t>
+    <t>This StructureDefinition contains the maps for VistA file V HEALTH FACTORS (#9000010.23) to us-core-smokingstatus</t>
   </si>
   <si>
     <t>Purpose</t>
